--- a/PCB/buying_componets.xlsx
+++ b/PCB/buying_componets.xlsx
@@ -8,25 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deuter/repos/Smart-ball/PCB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A478CB1-99CD-3043-B171-C0B854430DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6926CE-AC5B-274C-B00D-BC4FB5A327F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="620" windowWidth="38400" windowHeight="19100" activeTab="2" xr2:uid="{341A82F6-8500-7242-AEDD-50C73C9F364C}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19560" activeTab="5" xr2:uid="{341A82F6-8500-7242-AEDD-50C73C9F364C}"/>
   </bookViews>
   <sheets>
     <sheet name="wszystkie" sheetId="2" r:id="rId1"/>
-    <sheet name="bez R" sheetId="4" r:id="rId2"/>
-    <sheet name="zakupy_final" sheetId="5" r:id="rId3"/>
-    <sheet name="skladane jlc" sheetId="3" r:id="rId4"/>
-    <sheet name="do zakupu" sheetId="1" r:id="rId5"/>
+    <sheet name="R and C" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId3"/>
+    <sheet name="R_C_grouped" sheetId="7" r:id="rId4"/>
+    <sheet name="bez R" sheetId="4" r:id="rId5"/>
+    <sheet name="zakupy_final" sheetId="5" r:id="rId6"/>
+    <sheet name="skladane jlc" sheetId="3" r:id="rId7"/>
+    <sheet name="do zakupu" sheetId="1" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="bom" localSheetId="1">'bez R'!$A$1:$E$35</definedName>
+    <definedName name="bom" localSheetId="4">'bez R'!$A$1:$E$35</definedName>
     <definedName name="bom" localSheetId="0">wszystkie!$A$1:$E$35</definedName>
-    <definedName name="bom" localSheetId="2">zakupy_final!$A$1:$E$16</definedName>
-    <definedName name="bom_1" localSheetId="1">'bez R'!$A$38:$E$87</definedName>
+    <definedName name="bom" localSheetId="5">zakupy_final!$A$1:$E$16</definedName>
+    <definedName name="bom_1" localSheetId="4">'bez R'!$A$38:$E$87</definedName>
     <definedName name="bom_1" localSheetId="0">wszystkie!$A$38:$E$87</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId9"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -107,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="200">
   <si>
     <t>Designator</t>
   </si>
@@ -695,13 +701,25 @@
   </si>
   <si>
     <t>ferrat bead</t>
+  </si>
+  <si>
+    <t>Sum of Quantity</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>anteny gps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -719,6 +737,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -753,10 +779,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -765,8 +792,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -780,6 +819,644 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>92763</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E4DAC54-9AC3-EB06-9CD6-329F6031123C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10363200"/>
+          <a:ext cx="7772400" cy="3953563"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>170495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7D784D6-8250-3B65-ED89-6839622A57D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14427200"/>
+          <a:ext cx="7772400" cy="3421695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{690CAA9E-4B4D-F765-295E-DD91C751C3D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="18084800"/>
+          <a:ext cx="7772400" cy="1932214"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>37463</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785052D5-6068-47D6-8AF4-DE8CABEB2774}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20116800"/>
+          <a:ext cx="7772400" cy="2679063"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Szymon Mamok" refreshedDate="46142.365134143518" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="37" xr:uid="{92433B2F-10D0-C546-885D-6754CE4BBD6F}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:C38" sheet="R_C_grouped"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Footprint" numFmtId="0">
+      <sharedItems count="3">
+        <s v="C_Disc_D5.0mm_W2.5mm_P2.50mm"/>
+        <s v="CP_Radial_Tantal_D5.0mm_P2.50mm"/>
+        <s v="R_Axial_DIN0207_L6.3mm_D2.5mm_P7.62mm_Horizontal"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="6"/>
+    </cacheField>
+    <cacheField name="Value" numFmtId="0">
+      <sharedItems count="36">
+        <s v="1μF"/>
+        <s v="0F"/>
+        <s v="100nF"/>
+        <s v="1000nF"/>
+        <s v="1000µF"/>
+        <s v="100µF"/>
+        <s v="100 nF"/>
+        <s v="10μF"/>
+        <s v="10µF"/>
+        <s v="0.1μF"/>
+        <s v="C1"/>
+        <s v="22µF"/>
+        <s v="1µF"/>
+        <s v="0.47µF"/>
+        <s v="C2"/>
+        <s v="20µF"/>
+        <s v="4.7µF"/>
+        <s v="0.1µF"/>
+        <s v="2.2µF"/>
+        <s v="220µF"/>
+        <s v="1kΩ"/>
+        <s v="1.5kΩ"/>
+        <s v="100kΩ"/>
+        <s v="66Ω"/>
+        <s v="10Ω"/>
+        <s v="200Ω"/>
+        <s v="20kΩ"/>
+        <s v="1MΩ"/>
+        <s v="5.1kΩ"/>
+        <s v="180kΩ"/>
+        <s v="4.7kΩ"/>
+        <s v="10kΩ"/>
+        <s v="330kΩ"/>
+        <s v="110kΩ"/>
+        <s v="200kΩ"/>
+        <s v="750kΩ"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="37">
+  <r>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="6"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="25"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="26"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="27"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="28"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="29"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="30"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="31"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="32"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="33"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="34"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="35"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B92A8506-790C-FC48-B4DD-4D6B2B645238}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="37">
+        <item x="9"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="21"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="31"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="24"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="34"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="15"/>
+        <item x="19"/>
+        <item x="11"/>
+        <item x="32"/>
+        <item x="30"/>
+        <item x="16"/>
+        <item x="28"/>
+        <item x="23"/>
+        <item x="35"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="41">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="33"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quantity" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1119,21 +1796,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78988CE1-F9E6-DB4F-89CF-CE27463C469F}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1142,15 +1819,12 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>93</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C2">
@@ -1160,11 +1834,11 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>96</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C3">
@@ -1174,11 +1848,11 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>98</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C4">
@@ -1188,11 +1862,11 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>100</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C5">
@@ -1202,11 +1876,11 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C6">
@@ -1216,11 +1890,11 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>105</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C7">
@@ -1230,11 +1904,11 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>107</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C8">
@@ -1244,25 +1918,25 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>108</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10">
@@ -1272,11 +1946,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>110</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C11">
@@ -1286,11 +1960,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>805</v>
       </c>
       <c r="C12">
@@ -1300,11 +1974,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13">
@@ -1314,11 +1988,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C14">
@@ -1328,11 +2002,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C15">
@@ -1342,11 +2016,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C16">
@@ -1356,11 +2030,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C17">
@@ -1370,11 +2044,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C18">
@@ -1384,11 +2058,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C19">
@@ -1398,11 +2072,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C20">
@@ -1412,11 +2086,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C21">
@@ -1426,11 +2100,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>36</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C22">
@@ -1440,11 +2114,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C23">
@@ -1454,11 +2128,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>113</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C24">
@@ -1468,11 +2142,11 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>116</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C25">
@@ -1482,11 +2156,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>118</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C26">
@@ -1496,11 +2170,11 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>120</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C27">
@@ -1514,7 +2188,7 @@
       <c r="A28" t="s">
         <v>44</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>18259106</v>
       </c>
       <c r="C28">
@@ -1524,11 +2198,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>122</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C29">
@@ -1538,11 +2212,11 @@
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>125</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C30">
@@ -1552,11 +2226,11 @@
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>127</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C31">
@@ -1566,11 +2240,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>129</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C32">
@@ -1580,11 +2254,11 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>131</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C33">
@@ -1594,11 +2268,11 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>133</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C34">
@@ -1608,11 +2282,11 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>42</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C35">
@@ -1622,16 +2296,16 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>0</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
@@ -1640,15 +2314,12 @@
       <c r="D38" t="s">
         <v>3</v>
       </c>
-      <c r="E38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>136</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C39">
@@ -1658,11 +2329,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>83</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C40">
@@ -1672,11 +2343,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>139</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C41">
@@ -1686,11 +2357,11 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>141</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C42">
@@ -1700,11 +2371,11 @@
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>143</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C43">
@@ -1714,11 +2385,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>145</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C44">
@@ -1728,11 +2399,11 @@
         <v>146</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>147</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C45">
@@ -1742,11 +2413,11 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>100</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C46">
@@ -1756,11 +2427,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>150</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C47">
@@ -1770,11 +2441,11 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>152</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C48">
@@ -1784,11 +2455,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>153</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C49">
@@ -1798,11 +2469,11 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>155</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C50">
@@ -1812,11 +2483,11 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>157</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C51">
@@ -1826,11 +2497,11 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>159</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C52">
@@ -1840,11 +2511,11 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>107</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C53">
@@ -1854,11 +2525,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>162</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C54">
@@ -1868,11 +2539,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>46</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C55">
@@ -1882,11 +2553,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>49</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C56">
@@ -1896,11 +2567,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C57">
@@ -1910,11 +2581,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>54</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C58">
@@ -1924,11 +2595,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>56</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C59">
@@ -1938,11 +2609,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C60">
@@ -1952,11 +2623,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>22</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C61">
@@ -1966,11 +2637,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>63</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C62">
@@ -1980,11 +2651,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>25</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C63">
@@ -1994,11 +2665,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>68</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C64">
@@ -2008,11 +2679,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>69</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C65">
@@ -2022,11 +2693,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>72</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C66">
@@ -2036,11 +2707,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>75</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C67">
@@ -2050,11 +2721,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>77</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C68">
@@ -2064,11 +2735,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>36</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C69">
@@ -2078,11 +2749,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>163</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C70">
@@ -2092,11 +2763,11 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>118</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C71">
@@ -2106,11 +2777,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>166</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C72">
@@ -2120,11 +2791,11 @@
         <v>115</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>167</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C73">
@@ -2134,11 +2805,11 @@
         <v>168</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>169</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C74">
@@ -2148,11 +2819,11 @@
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>171</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C75">
@@ -2162,11 +2833,11 @@
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>173</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C76">
@@ -2176,11 +2847,11 @@
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>175</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C77">
@@ -2190,11 +2861,11 @@
         <v>176</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>177</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C78">
@@ -2204,11 +2875,11 @@
         <v>178</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>179</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C79">
@@ -2218,11 +2889,11 @@
         <v>180</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>181</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C80">
@@ -2232,11 +2903,11 @@
         <v>182</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>183</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C81">
@@ -2246,11 +2917,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>184</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C82">
@@ -2260,11 +2931,11 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>186</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C83">
@@ -2274,11 +2945,11 @@
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>188</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C84">
@@ -2288,11 +2959,11 @@
         <v>189</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>190</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C85">
@@ -2302,11 +2973,11 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>78</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C86">
@@ -2316,11 +2987,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>42</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C87">
@@ -2332,10 +3003,1351 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="47" max="4" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07E3883-5DD7-1547-9D55-882948E21EE1}">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="37.5" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6F9AF1-DC2C-114A-8285-6C39A7041847}">
+  <dimension ref="A3:B44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6810B00-5A20-0545-820F-41F701AB74E9}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="39.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="5">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="5">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="5">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="5">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="5">
+        <v>4</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="5">
+        <v>3</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="5">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="5">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="5">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="5">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="5">
+        <v>4</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="5">
+        <v>1</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6894A1EC-1FE6-8E42-A3CF-3DFD43519E6A}">
   <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2945,23 +4957,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14FAB4D-03C6-E04F-B68A-E4321C7CFE0C}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -2974,11 +4987,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2">
@@ -2992,7 +5005,7 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>805</v>
       </c>
       <c r="C3">
@@ -3005,11 +5018,11 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -3019,11 +5032,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C5">
@@ -3033,11 +5046,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C6">
@@ -3047,11 +5060,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C7">
@@ -3061,11 +5074,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C8">
@@ -3075,11 +5088,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C9">
@@ -3089,11 +5102,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C10">
@@ -3103,11 +5116,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C12">
@@ -3117,11 +5130,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C13">
@@ -3131,11 +5144,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C14">
@@ -3149,7 +5162,7 @@
       <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>18259106</v>
       </c>
       <c r="C15">
@@ -3159,11 +5172,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C16">
@@ -3178,11 +5191,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
@@ -3195,11 +5208,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>136</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C20">
@@ -3209,11 +5222,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>83</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C21">
@@ -3223,11 +5236,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C23">
@@ -3237,11 +5250,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>49</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C24">
@@ -3251,11 +5264,11 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C25">
@@ -3265,11 +5278,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C26">
@@ -3279,11 +5292,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>56</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C27">
@@ -3293,11 +5306,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>59</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C28">
@@ -3307,11 +5320,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>22</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C29">
@@ -3321,11 +5334,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C30">
@@ -3335,11 +5348,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C31">
@@ -3349,11 +5362,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>68</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C32">
@@ -3363,11 +5376,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>69</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C33">
@@ -3377,11 +5390,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>42</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C39">
@@ -3391,34 +5404,53 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+    <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="10" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
+    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>194</v>
       </c>
     </row>
+    <row r="47" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D42" r:id="rId1" display="https://www.tme.eu/pl/details/u.fl-r-smt-01-/zlacza-mikro/hirose/u-fl-r-smt-01/?brutto=1&amp;currency=PLN&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=Z%C5%82%C4%85cza%20PL%20%5BPLA%5D%20CSS%20Segment_A&amp;utm_content=&amp;campaign_id=11197053321&amp;gad_source=1&amp;gad_campaignid=11197053321&amp;gbraid=0AAAAADyylhKMkvE7UhyokF-BE3LuKHIJY&amp;gclid=CjwKCAjw14zPBhAuEiwAP3-Eb2XtyXj2WBAtxhoOsPP-QF8nj4mjBUo6L4n3zQlIyrJ-SGP66PuGGhoCb9YQAvD_BwE" xr:uid="{CAA9024D-6412-F34C-8872-49647B10133E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="98" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="2"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="4" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CC1FF1-90E4-B144-87DD-CEDDE4BDFA30}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB7FB89-158E-A040-A172-E01ED619FA97}">
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3789,5 +5821,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>